--- a/data/trans_orig/P2A_fisi_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P2A_fisi_R-Estudios-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4817</t>
+          <t>5170</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>589</t>
+          <t>595</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5731</t>
+          <t>5867</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>1277</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7977</t>
+          <t>7909</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,33%</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>51645</t>
+          <t>51292</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>90,84%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>45640</t>
+          <t>45504</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>50782</t>
+          <t>50776</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,84%</t>
+          <t>88,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>99856</t>
+          <t>99924</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>106532</t>
+          <t>106556</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,82%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2787</t>
+          <t>2744</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11011</t>
+          <t>11085</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6636</t>
+          <t>6819</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17130</t>
+          <t>17248</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11030</t>
+          <t>11207</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>24219</t>
+          <t>24273</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,66%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>299306</t>
+          <t>299232</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>307530</t>
+          <t>307573</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>336506</t>
+          <t>336388</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>347000</t>
+          <t>346817</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>639734</t>
+          <t>639680</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>652923</t>
+          <t>652746</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,31%</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4217</t>
+          <t>5108</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2569</t>
+          <t>2579</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10161</t>
+          <t>9573</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>3341</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12075</t>
+          <t>12089</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,65%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>132364</t>
+          <t>131473</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>113381</t>
+          <t>113969</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>120973</t>
+          <t>120963</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>248048</t>
+          <t>248034</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>256830</t>
+          <t>256782</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,72%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4835</t>
+          <t>5012</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14749</t>
+          <t>15030</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11828</t>
+          <t>12140</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>25565</t>
+          <t>26620</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>20139</t>
+          <t>19548</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>37367</t>
+          <t>36688</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,56%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>488610</t>
+          <t>488329</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>498524</t>
+          <t>498347</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>502984</t>
+          <t>501929</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>516721</t>
+          <t>516409</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>994541</t>
+          <t>995220</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1011769</t>
+          <t>1012360</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,11%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>684</t>
+          <t>719</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5979</t>
+          <t>5707</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>628</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6478</t>
+          <t>5901</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1985</t>
+          <t>1995</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9382</t>
+          <t>9605</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,17%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>49505</t>
+          <t>49777</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>54800</t>
+          <t>54765</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,22%</t>
+          <t>89,71%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>55612</t>
+          <t>56189</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>61454</t>
+          <t>61462</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,57%</t>
+          <t>90,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>108192</t>
+          <t>107969</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>115589</t>
+          <t>115579</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,02%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,3%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4898</t>
+          <t>4793</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14930</t>
+          <t>14674</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10114</t>
+          <t>10013</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22481</t>
+          <t>21729</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17103</t>
+          <t>16714</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>32447</t>
+          <t>32767</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,08%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>289723</t>
+          <t>289979</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>299755</t>
+          <t>299860</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>317312</t>
+          <t>318064</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>329679</t>
+          <t>329780</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>611999</t>
+          <t>611679</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>627343</t>
+          <t>627732</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,41%</t>
         </is>
       </c>
     </row>
@@ -3027,7 +3027,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5761</t>
+          <t>5112</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3062,7 +3062,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5072</t>
+          <t>5026</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1113</t>
+          <t>1013</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7662</t>
+          <t>7951</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,13%</t>
         </is>
       </c>
     </row>
@@ -3135,7 +3135,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>111066</t>
+          <t>111715</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>131826</t>
+          <t>131872</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>246063</t>
+          <t>245774</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>252612</t>
+          <t>252712</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,6%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8417</t>
+          <t>8595</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21328</t>
+          <t>20541</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13359</t>
+          <t>12767</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>27717</t>
+          <t>27542</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>23632</t>
+          <t>24241</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>41632</t>
+          <t>42138</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,15%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>455637</t>
+          <t>456424</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>468548</t>
+          <t>468370</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>511064</t>
+          <t>511239</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>525422</t>
+          <t>526014</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>974114</t>
+          <t>973608</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>992114</t>
+          <t>991505</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,61%</t>
         </is>
       </c>
     </row>
@@ -3944,7 +3944,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4159</t>
+          <t>4170</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3959,7 +3959,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>628</t>
+          <t>640</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6188</t>
+          <t>5970</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1230</t>
+          <t>1210</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7673</t>
+          <t>7406</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,06%</t>
         </is>
       </c>
     </row>
@@ -4052,7 +4052,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>36482</t>
+          <t>36471</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,77%</t>
+          <t>89,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>45049</t>
+          <t>45267</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>50609</t>
+          <t>50597</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,92%</t>
+          <t>88,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>84205</t>
+          <t>84472</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>90648</t>
+          <t>90668</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,68%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3369</t>
+          <t>3286</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11417</t>
+          <t>12334</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4638</t>
+          <t>4526</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15232</t>
+          <t>14793</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9751</t>
+          <t>9902</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>23025</t>
+          <t>23073</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,17%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>337305</t>
+          <t>336388</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>345353</t>
+          <t>345436</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>364634</t>
+          <t>365073</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>375228</t>
+          <t>375340</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>705563</t>
+          <t>705515</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>718837</t>
+          <t>718686</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,64%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2589</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11994</t>
+          <t>11707</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>591</t>
+          <t>596</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5443</t>
+          <t>5556</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3619</t>
+          <t>4363</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14037</t>
+          <t>14872</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,39%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>124033</t>
+          <t>124320</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>133683</t>
+          <t>133438</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,18%</t>
+          <t>91,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>134487</t>
+          <t>134374</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>139339</t>
+          <t>139334</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>261920</t>
+          <t>261085</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>272338</t>
+          <t>271594</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,42%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8157</t>
+          <t>8253</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21193</t>
+          <t>21186</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,7 +4983,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7533</t>
+          <t>7317</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18987</t>
+          <t>19810</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5043,7 +5043,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>36896</t>
+          <t>36956</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>504197</t>
+          <t>504204</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>517233</t>
+          <t>517137</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>552046</t>
+          <t>551223</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>563500</t>
+          <t>563716</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1059527</t>
+          <t>1059467</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1463</t>
+          <t>1313</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7956</t>
+          <t>7884</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2460</t>
+          <t>2420</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10115</t>
+          <t>10111</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5088</t>
+          <t>4709</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14279</t>
+          <t>14415</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,35%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>46722</t>
+          <t>46794</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>53215</t>
+          <t>53365</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,45%</t>
+          <t>85,58%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>51889</t>
+          <t>51893</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>59544</t>
+          <t>59584</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5710,7 +5710,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>102403</t>
+          <t>102267</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>111594</t>
+          <t>111973</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,76%</t>
+          <t>87,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,96%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18565</t>
+          <t>19224</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>36964</t>
+          <t>36461</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25467</t>
+          <t>25453</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>52850</t>
+          <t>51158</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5940,7 +5940,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>48713</t>
+          <t>49770</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>79641</t>
+          <t>79384</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,12%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>423546</t>
+          <t>424049</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>441945</t>
+          <t>441286</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>92,08%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>463769</t>
+          <t>465461</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>491152</t>
+          <t>491166</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,7 +6048,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,77%</t>
+          <t>90,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>897488</t>
+          <t>897745</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>928416</t>
+          <t>927359</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>91,88%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>94,91%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1640</t>
+          <t>1621</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7306</t>
+          <t>7377</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2058</t>
+          <t>1925</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12444</t>
+          <t>11784</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5051</t>
+          <t>5061</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16030</t>
+          <t>15544</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6318,7 +6318,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,67%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>142245</t>
+          <t>142174</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>147911</t>
+          <t>147930</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>170905</t>
+          <t>171565</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>181291</t>
+          <t>181424</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>316870</t>
+          <t>317356</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>327849</t>
+          <t>327839</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,7 +6426,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>24920</t>
+          <t>26008</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>44525</t>
+          <t>45035</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>34970</t>
+          <t>34286</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>62420</t>
+          <t>61958</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>65556</t>
+          <t>64565</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>99978</t>
+          <t>98776</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,92%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>620213</t>
+          <t>619703</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>639818</t>
+          <t>638730</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>699552</t>
+          <t>700014</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>727002</t>
+          <t>727686</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1326732</t>
+          <t>1327934</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1361154</t>
+          <t>1362145</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>93,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,47%</t>
         </is>
       </c>
     </row>
